--- a/results/02_taxa_assemblage/AU-Sweeping/tables/k2_popout_atypical_sites.xlsx
+++ b/results/02_taxa_assemblage/AU-Sweeping/tables/k2_popout_atypical_sites.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,23 +466,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DR-94</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7347</v>
+        <v>0.9044</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3816</v>
+        <v>0.5891</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3531</v>
+        <v>0.3153</v>
       </c>
     </row>
     <row r="3">
@@ -491,23 +491,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SCR-02</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.9044</v>
       </c>
       <c r="F3" t="n">
-        <v>0.056</v>
+        <v>0.5589</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5766</v>
+        <v>0.3455</v>
       </c>
     </row>
     <row r="4">
@@ -516,23 +516,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6431</v>
+        <v>0.9526</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2512</v>
+        <v>0.5804</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3919</v>
+        <v>0.3722</v>
       </c>
     </row>
     <row r="5">
@@ -541,23 +541,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LSC-31</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6431</v>
+        <v>0.8814</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0036</v>
+        <v>0.2195</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6395</v>
+        <v>0.6619</v>
       </c>
     </row>
     <row r="6">
@@ -566,23 +566,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DR-110</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4339</v>
+        <v>0.9301</v>
       </c>
       <c r="F6" t="n">
-        <v>0.062</v>
+        <v>0.034</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3719</v>
+        <v>0.8961</v>
       </c>
     </row>
     <row r="7">
@@ -591,23 +591,148 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D7" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.9621</v>
       </c>
       <c r="F7" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8581</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LSC-32</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>58</v>
+      </c>
+      <c r="D8" t="n">
+        <v>51</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4769</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5117</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LSC-28</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>62</v>
+      </c>
+      <c r="D9" t="n">
+        <v>54</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9636</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DR-110</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>63</v>
+      </c>
+      <c r="D10" t="n">
+        <v>54</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9636</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LSC-29</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>66</v>
+      </c>
+      <c r="D11" t="n">
+        <v>56</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7663</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.062</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.753</v>
+      <c r="G11" t="n">
+        <v>0.7043</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DR-71</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>68</v>
+      </c>
+      <c r="D12" t="n">
+        <v>57</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7717000000000001</v>
       </c>
     </row>
   </sheetData>
